--- a/artfynd/A 73935-2021 artfynd.xlsx
+++ b/artfynd/A 73935-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 73935-2021 artfynd.xlsx
+++ b/artfynd/A 73935-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>103417731</v>
       </c>
       <c r="B2" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +700,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445245.8173556555</v>
+        <v>445246</v>
       </c>
       <c r="R2" t="n">
-        <v>7097773.135857749</v>
+        <v>7097773</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-09-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,50 +772,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103417728</v>
+        <v>103417723</v>
       </c>
       <c r="B3" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grubbdalen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445495.23774881</v>
+        <v>445600</v>
       </c>
       <c r="R3" t="n">
-        <v>7097109.525726979</v>
+        <v>7097120</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +848,14 @@
           <t>2022-09-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-04</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +885,7 @@
         <v>103417724</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445576.2097941383</v>
+        <v>445576</v>
       </c>
       <c r="R4" t="n">
-        <v>7097165.613693597</v>
+        <v>7097166</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +958,9 @@
           <t>2022-09-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1024,15 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103417723</v>
+        <v>103417725</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,7 +1025,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1072,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445600.0264993102</v>
+        <v>445486</v>
       </c>
       <c r="R5" t="n">
-        <v>7097119.986368139</v>
+        <v>7097061</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,19 +1068,9 @@
           <t>2022-09-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1152,12 +1105,7 @@
         <v>103417726</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445505.6395759351</v>
+        <v>445505</v>
       </c>
       <c r="R6" t="n">
-        <v>7097075.983257764</v>
+        <v>7097076</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,19 +1178,9 @@
           <t>2022-09-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1274,58 +1212,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99019545</v>
+        <v>103417728</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Grubbdalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443503.4304674634</v>
+        <v>445495</v>
       </c>
       <c r="R7" t="n">
-        <v>7098401.908944439</v>
+        <v>7097110</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,22 +1277,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-03-08</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-03-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,50 +1309,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103672752</v>
+        <v>99019545</v>
       </c>
       <c r="B8" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Klockansexklumpen, 0,8 km NV om bergets högsta topp, Jmt</t>
+          <t>Grubbdalen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441744.0179928062</v>
+        <v>443504</v>
       </c>
       <c r="R8" t="n">
-        <v>7098671.677853395</v>
+        <v>7098402</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,22 +1382,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,24 +1398,230 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Fjällbarrskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>99019520</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Grubbdalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>443508</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7098403</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-03-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-03-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>103672752</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Klockansexklumpen, 0,8 km NV om bergets högsta topp, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>441744</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7098671</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Fjällbarrskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Ola Löfgren</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Ola Löfgren</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 73935-2021 artfynd.xlsx
+++ b/artfynd/A 73935-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103417731</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103417723</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103417724</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103417725</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103417726</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103417728</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1408,6 +1443,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103672752</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1513,6 +1553,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99019545</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1622,8 +1667,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99019520</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>